--- a/output/pdf_financials_xlsx/ARMY.xlsx
+++ b/output/pdf_financials_xlsx/ARMY.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000878</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007523</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>-4.63238</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.482679</v>
+        <v>-5.483557</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.673399</v>
+        <v>-0.680922</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.29131</v>
@@ -981,10 +981,10 @@
         <v>-4.63238</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.482679</v>
+        <v>-5.483557</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.673399</v>
+        <v>-0.680922</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.29131</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.128622</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.023775</v>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.128622</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.023775</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.013316</v>
+        <v>0.884694</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.236842</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">

--- a/output/pdf_financials_xlsx/ARMY.xlsx
+++ b/output/pdf_financials_xlsx/ARMY.xlsx
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.027485</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -4510,7 +4510,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -6694,7 +6698,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>-0.027485</v>
       </c>
@@ -6730,7 +6738,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>3.874762</v>
       </c>
